--- a/artfynd/A 49050-2025 artfynd.xlsx
+++ b/artfynd/A 49050-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121492672</v>
+        <v>121492671</v>
       </c>
       <c r="B2" t="n">
-        <v>56572</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stenkullafors-Åsele, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613440</v>
+        <v>613441</v>
       </c>
       <c r="R2" t="n">
-        <v>7121670</v>
+        <v>7121652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -783,6 +773,221 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121492687</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613420</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7121652</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121492672</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenkullafors-Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613440</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7121670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
         </is>
